--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/15gps/6mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/15gps/6mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X49"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.56550969907</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>677.2192760788672</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>679.0368946356135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24">
+        <v>0.240636706</v>
+      </c>
+      <c r="Y2">
+        <v>0.261051872</v>
+      </c>
+      <c r="Z2">
+        <v>0.3550409893931049</v>
+      </c>
+      <c r="AA2">
+        <v>10.207583</v>
+      </c>
+      <c r="AB2">
+        <v>0.03619106562987214</v>
+      </c>
+      <c r="AC2">
+        <v>24.50928726638478</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.56562543981</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>680.9733241030823</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24">
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>679.0002490210588</v>
+      </c>
+      <c r="X3">
+        <v>0.240576742</v>
+      </c>
+      <c r="Y3">
+        <v>0.261049326</v>
+      </c>
+      <c r="Z3">
+        <v>0.3549984780198203</v>
+      </c>
+      <c r="AA3">
+        <v>10.236292</v>
+      </c>
+      <c r="AB3">
+        <v>0.03609333224756667</v>
+      </c>
+      <c r="AC3">
+        <v>24.57859643858245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.56574118056</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>681.0572592593727</v>
       </c>
-      <c r="V4">
-        <v>2.192032412032948</v>
-      </c>
-      <c r="W4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24">
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.24054121</v>
+      </c>
+      <c r="Y4">
+        <v>0.26104137</v>
+      </c>
+      <c r="Z4">
+        <v>0.3549685486909242</v>
+      </c>
+      <c r="AA4">
+        <v>10.25008</v>
+      </c>
+      <c r="AB4">
+        <v>0.0360457048375142</v>
+      </c>
+      <c r="AC4">
+        <v>24.54918894470973</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.5658575</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>680.6269912300698</v>
       </c>
-      <c r="V5">
-        <v>0.2280797179467783</v>
-      </c>
-      <c r="W5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24">
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>24.55416525093069</v>
+      </c>
+      <c r="X5">
+        <v>0.240515512</v>
+      </c>
+      <c r="Y5">
+        <v>0.261039142</v>
+      </c>
+      <c r="Z5">
+        <v>0.3549494966452527</v>
+      </c>
+      <c r="AA5">
+        <v>10.261815</v>
+      </c>
+      <c r="AB5">
+        <v>0.03600587506053415</v>
+      </c>
+      <c r="AC5">
+        <v>24.50657040905717</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.56597381944</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>681.6467127891256</v>
       </c>
-      <c r="V6">
-        <v>0.5119274197876644</v>
-      </c>
-      <c r="W6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24">
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>0.240514242</v>
+      </c>
+      <c r="Y6">
+        <v>0.26105028</v>
+      </c>
+      <c r="Z6">
+        <v>0.3549568273648401</v>
+      </c>
+      <c r="AA6">
+        <v>10.268019</v>
+      </c>
+      <c r="AB6">
+        <v>0.03598648445305723</v>
+      </c>
+      <c r="AC6">
+        <v>24.53006883226344</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.56608956018</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>681.8108675966128</v>
       </c>
-      <c r="V7">
-        <v>0.6413971871475359</v>
-      </c>
-      <c r="W7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24">
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>0.240531374</v>
+      </c>
+      <c r="Y7">
+        <v>0.261039778</v>
+      </c>
+      <c r="Z7">
+        <v>0.3549607127227141</v>
+      </c>
+      <c r="AA7">
+        <v>10.254202</v>
+      </c>
+      <c r="AB7">
+        <v>0.0360315963836504</v>
+      </c>
+      <c r="AC7">
+        <v>24.56673399122765</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.56620587963</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>680.2949897375597</v>
       </c>
-      <c r="V8">
-        <v>0.8318641408031281</v>
-      </c>
-      <c r="W8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>0.240540892</v>
+      </c>
+      <c r="Y8">
+        <v>0.261029594</v>
+      </c>
+      <c r="Z8">
+        <v>0.3549596732981938</v>
+      </c>
+      <c r="AA8">
+        <v>10.244351</v>
+      </c>
+      <c r="AB8">
+        <v>0.03606347940085892</v>
+      </c>
+      <c r="AC8">
+        <v>24.53380434890802</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.56632162037</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>678.25048698207</v>
       </c>
-      <c r="V9">
-        <v>1.786718935236048</v>
-      </c>
-      <c r="W9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>0.240553266</v>
+      </c>
+      <c r="Y9">
+        <v>0.261012726</v>
+      </c>
+      <c r="Z9">
+        <v>0.354955654860178</v>
+      </c>
+      <c r="AA9">
+        <v>10.22973</v>
+      </c>
+      <c r="AB9">
+        <v>0.03611068564768083</v>
+      </c>
+      <c r="AC9">
+        <v>24.49209012579597</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.56643793981</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>681.0357607557017</v>
       </c>
-      <c r="V10">
-        <v>1.442595069808069</v>
-      </c>
-      <c r="W10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>0.24056786</v>
+      </c>
+      <c r="Y10">
+        <v>0.261015272</v>
+      </c>
+      <c r="Z10">
+        <v>0.3549674174937942</v>
+      </c>
+      <c r="AA10">
+        <v>10.223706</v>
+      </c>
+      <c r="AB10">
+        <v>0.03613143706582165</v>
+      </c>
+      <c r="AC10">
+        <v>24.60680072931861</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.56655425926</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>679.3408104871504</v>
       </c>
-      <c r="V11">
-        <v>1.403531958588547</v>
-      </c>
-      <c r="W11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24">
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>0.240569762</v>
+      </c>
+      <c r="Y11">
+        <v>0.26101177</v>
+      </c>
+      <c r="Z11">
+        <v>0.3549661314368873</v>
+      </c>
+      <c r="AA11">
+        <v>10.221004</v>
+      </c>
+      <c r="AB11">
+        <v>0.03614013620719444</v>
+      </c>
+      <c r="AC11">
+        <v>24.55146942211148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.5666705787</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>682.1350206515795</v>
       </c>
-      <c r="V12">
-        <v>1.407648107929619</v>
-      </c>
-      <c r="W12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>0.240559928</v>
+      </c>
+      <c r="Y12">
+        <v>0.260992674</v>
+      </c>
+      <c r="Z12">
+        <v>0.3549454251586227</v>
+      </c>
+      <c r="AA12">
+        <v>10.216373</v>
+      </c>
+      <c r="AB12">
+        <v>0.03615331653763523</v>
+      </c>
+      <c r="AC12">
+        <v>24.6614433230229</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.56678631945</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>676.0579939264572</v>
       </c>
-      <c r="V13">
-        <v>3.041785353812577</v>
-      </c>
-      <c r="W13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>0.240582136</v>
+      </c>
+      <c r="Y13">
+        <v>0.260978672</v>
+      </c>
+      <c r="Z13">
+        <v>0.3549501815765222</v>
+      </c>
+      <c r="AA13">
+        <v>10.198268</v>
+      </c>
+      <c r="AB13">
+        <v>0.03621304137087116</v>
+      </c>
+      <c r="AC13">
+        <v>24.48211610316696</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.56690263889</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>676.1958854542601</v>
       </c>
-      <c r="V14">
-        <v>3.469452281060423</v>
-      </c>
-      <c r="W14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24">
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>0.240592288</v>
+      </c>
+      <c r="Y14">
+        <v>0.260968806</v>
+      </c>
+      <c r="Z14">
+        <v>0.3549498087760304</v>
+      </c>
+      <c r="AA14">
+        <v>10.188259</v>
+      </c>
+      <c r="AB14">
+        <v>0.03624587046516863</v>
+      </c>
+      <c r="AC14">
+        <v>24.50930847325512</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.56701895833</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>675.3830423332702</v>
       </c>
-      <c r="V15">
-        <v>0.4349880584442731</v>
-      </c>
-      <c r="W15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24">
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>0.240584992</v>
+      </c>
+      <c r="Y15">
+        <v>0.26096594</v>
+      </c>
+      <c r="Z15">
+        <v>0.3549427562519394</v>
+      </c>
+      <c r="AA15">
+        <v>10.190474</v>
+      </c>
+      <c r="AB15">
+        <v>0.03623792661151897</v>
+      </c>
+      <c r="AC15">
+        <v>24.47448112273745</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.56713527778</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>678.0782109029932</v>
       </c>
-      <c r="V16">
-        <v>1.382497537883259</v>
-      </c>
-      <c r="W16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23">
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>0.240552948</v>
+      </c>
+      <c r="Y16">
+        <v>0.260956712</v>
+      </c>
+      <c r="Z16">
+        <v>0.3549142520797687</v>
+      </c>
+      <c r="AA16">
+        <v>10.201882</v>
+      </c>
+      <c r="AB16">
+        <v>0.03619780655151179</v>
+      </c>
+      <c r="AC16">
+        <v>24.54494390506176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.56725159723</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>679.9080738145926</v>
       </c>
-      <c r="V17">
-        <v>2.276263085316086</v>
-      </c>
-      <c r="W17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>0.24050758</v>
+      </c>
+      <c r="Y17">
+        <v>0.260941434</v>
+      </c>
+      <c r="Z17">
+        <v>0.3548722700006761</v>
+      </c>
+      <c r="AA17">
+        <v>10.216927</v>
+      </c>
+      <c r="AB17">
+        <v>0.03614462540046272</v>
+      </c>
+      <c r="AC17">
+        <v>24.57502263477861</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.56736733796</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>677.5007840028094</v>
       </c>
-      <c r="V18">
-        <v>1.256772608590821</v>
-      </c>
-      <c r="W18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>0.240520904</v>
+      </c>
+      <c r="Y18">
+        <v>0.26092584</v>
+      </c>
+      <c r="Z18">
+        <v>0.3548698342219057</v>
+      </c>
+      <c r="AA18">
+        <v>10.202468</v>
+      </c>
+      <c r="AB18">
+        <v>0.03619170196530364</v>
+      </c>
+      <c r="AC18">
+        <v>24.51990645588923</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.5674830787</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>677.5531353238105</v>
       </c>
-      <c r="V19">
-        <v>1.374986072299189</v>
-      </c>
-      <c r="W19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23">
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>0.24052725</v>
+      </c>
+      <c r="Y19">
+        <v>0.260934752</v>
+      </c>
+      <c r="Z19">
+        <v>0.3548806881106155</v>
+      </c>
+      <c r="AA19">
+        <v>10.203751</v>
+      </c>
+      <c r="AB19">
+        <v>0.03618852102901506</v>
+      </c>
+      <c r="AC19">
+        <v>24.5196458859408</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.56759939815</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>677.5223131501388</v>
       </c>
-      <c r="V20">
-        <v>0.02631277064707671</v>
-      </c>
-      <c r="W20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23">
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>0.240524078</v>
+      </c>
+      <c r="Y20">
+        <v>0.26092775</v>
+      </c>
+      <c r="Z20">
+        <v>0.3548733898418034</v>
+      </c>
+      <c r="AA20">
+        <v>10.201836</v>
+      </c>
+      <c r="AB20">
+        <v>0.03619410782289431</v>
+      </c>
+      <c r="AC20">
+        <v>24.52231565457289</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.56771513889</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>679.3006333862365</v>
       </c>
-      <c r="V21">
-        <v>1.017932737356713</v>
-      </c>
-      <c r="W21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23">
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>0.240526298</v>
+      </c>
+      <c r="Y21">
+        <v>0.260938252</v>
+      </c>
+      <c r="Z21">
+        <v>0.3548826163485615</v>
+      </c>
+      <c r="AA21">
+        <v>10.205977</v>
+      </c>
+      <c r="AB21">
+        <v>0.03618141237303608</v>
+      </c>
+      <c r="AC21">
+        <v>24.57805634181203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.56783087963</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>678.6537513098598</v>
       </c>
-      <c r="V22">
-        <v>0.9000955127218055</v>
-      </c>
-      <c r="W22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23">
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>0.240513924</v>
+      </c>
+      <c r="Y22">
+        <v>0.260931886</v>
+      </c>
+      <c r="Z22">
+        <v>0.3548695489463625</v>
+      </c>
+      <c r="AA22">
+        <v>10.208981</v>
+      </c>
+      <c r="AB22">
+        <v>0.03617034923988756</v>
+      </c>
+      <c r="AC22">
+        <v>24.54714319783743</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.56794662037</v>
       </c>
@@ -2050,14 +2416,29 @@
       <c r="U23">
         <v>677.782387281625</v>
       </c>
-      <c r="V23">
-        <v>0.7618839505477097</v>
-      </c>
-      <c r="W23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23">
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>0.240510118</v>
+      </c>
+      <c r="Y23">
+        <v>0.260925522</v>
+      </c>
+      <c r="Z23">
+        <v>0.3548622900384689</v>
+      </c>
+      <c r="AA23">
+        <v>10.207702</v>
+      </c>
+      <c r="AB23">
+        <v>0.03617385149723285</v>
+      </c>
+      <c r="AC23">
+        <v>24.51799942496547</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" s="1">
         <v>46068.56806293981</v>
       </c>
@@ -2121,14 +2502,29 @@
       <c r="U24">
         <v>679.6648034371839</v>
       </c>
-      <c r="V24">
-        <v>0.9420714991073896</v>
-      </c>
-      <c r="W24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23">
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>0.24053645</v>
+      </c>
+      <c r="Y24">
+        <v>0.260937616</v>
+      </c>
+      <c r="Z24">
+        <v>0.35488902944775</v>
+      </c>
+      <c r="AA24">
+        <v>10.200583</v>
+      </c>
+      <c r="AB24">
+        <v>0.03619968794733069</v>
+      </c>
+      <c r="AC24">
+        <v>24.6036537932099</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" s="1">
         <v>46068.56817868056</v>
       </c>
@@ -2192,14 +2588,29 @@
       <c r="U25">
         <v>677.1339677616679</v>
       </c>
-      <c r="V25">
-        <v>1.314601820136815</v>
-      </c>
-      <c r="W25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23">
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="X25">
+        <v>0.240540892</v>
+      </c>
+      <c r="Y25">
+        <v>0.26093507</v>
+      </c>
+      <c r="Z25">
+        <v>0.3548901681930067</v>
+      </c>
+      <c r="AA25">
+        <v>10.197089</v>
+      </c>
+      <c r="AB25">
+        <v>0.03621125258914706</v>
+      </c>
+      <c r="AC25">
+        <v>24.51986914330912</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="1">
         <v>46068.568295</v>
       </c>
@@ -2263,14 +2674,29 @@
       <c r="U26">
         <v>677.1909329577678</v>
       </c>
-      <c r="V26">
-        <v>1.445014959493837</v>
-      </c>
-      <c r="W26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23">
+      <c r="V26" t="b">
+        <v>1</v>
+      </c>
+      <c r="X26">
+        <v>0.240567542</v>
+      </c>
+      <c r="Y26">
+        <v>0.260949074</v>
+      </c>
+      <c r="Z26">
+        <v>0.354918527954486</v>
+      </c>
+      <c r="AA26">
+        <v>10.190766</v>
+      </c>
+      <c r="AB26">
+        <v>0.03623468219395602</v>
+      </c>
+      <c r="AC26">
+        <v>24.53779824035329</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="1">
         <v>46068.56841074074</v>
       </c>
@@ -2334,14 +2760,29 @@
       <c r="U27">
         <v>679.6191487076122</v>
       </c>
-      <c r="V27">
-        <v>1.418661405189877</v>
-      </c>
-      <c r="W27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23">
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="X27">
+        <v>0.240547872</v>
+      </c>
+      <c r="Y27">
+        <v>0.260957666</v>
+      </c>
+      <c r="Z27">
+        <v>0.3549115131520756</v>
+      </c>
+      <c r="AA27">
+        <v>10.204897</v>
+      </c>
+      <c r="AB27">
+        <v>0.03618767040877512</v>
+      </c>
+      <c r="AC27">
+        <v>24.5938337569234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29">
       <c r="A28" s="1">
         <v>46068.56852706018</v>
       </c>
@@ -2405,14 +2846,29 @@
       <c r="U28">
         <v>679.6219710086094</v>
       </c>
-      <c r="V28">
-        <v>1.402746454746163</v>
-      </c>
-      <c r="W28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23">
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="X28">
+        <v>0.240540892</v>
+      </c>
+      <c r="Y28">
+        <v>0.260963394</v>
+      </c>
+      <c r="Z28">
+        <v>0.3549109940987387</v>
+      </c>
+      <c r="AA28">
+        <v>10.211251</v>
+      </c>
+      <c r="AB28">
+        <v>0.0361668236231453</v>
+      </c>
+      <c r="AC28">
+        <v>24.57976795588274</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29">
       <c r="A29" s="1">
         <v>46068.56864280093</v>
       </c>
@@ -2476,14 +2932,29 @@
       <c r="U29">
         <v>678.4840147337433</v>
       </c>
-      <c r="V29">
-        <v>0.6561861508648642</v>
-      </c>
-      <c r="W29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23">
+      <c r="V29" t="b">
+        <v>1</v>
+      </c>
+      <c r="X29">
+        <v>0.240573888</v>
+      </c>
+      <c r="Y29">
+        <v>0.26096053</v>
+      </c>
+      <c r="Z29">
+        <v>0.3549312522240292</v>
+      </c>
+      <c r="AA29">
+        <v>10.193321</v>
+      </c>
+      <c r="AB29">
+        <v>0.0362274914411944</v>
+      </c>
+      <c r="AC29">
+        <v>24.5797738367539</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29">
       <c r="A30" s="1">
         <v>46068.56875912037</v>
       </c>
@@ -2547,14 +3018,29 @@
       <c r="U30">
         <v>675.9224117101139</v>
       </c>
-      <c r="V30">
-        <v>1.894883177457423</v>
-      </c>
-      <c r="W30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23">
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30">
+        <v>0.24060022</v>
+      </c>
+      <c r="Y30">
+        <v>0.260961804</v>
+      </c>
+      <c r="Z30">
+        <v>0.3549500373446703</v>
+      </c>
+      <c r="AA30">
+        <v>10.180792</v>
+      </c>
+      <c r="AB30">
+        <v>0.03627045338877611</v>
+      </c>
+      <c r="AC30">
+        <v>24.51601232836082</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29">
       <c r="A31" s="1">
         <v>46068.56887486111</v>
       </c>
@@ -2618,14 +3104,29 @@
       <c r="U31">
         <v>676.7660909888567</v>
       </c>
-      <c r="V31">
-        <v>1.305428842009855</v>
-      </c>
-      <c r="W31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23">
+      <c r="V31" t="b">
+        <v>1</v>
+      </c>
+      <c r="X31">
+        <v>0.240622112</v>
+      </c>
+      <c r="Y31">
+        <v>0.260962122</v>
+      </c>
+      <c r="Z31">
+        <v>0.3549651108237025</v>
+      </c>
+      <c r="AA31">
+        <v>10.170005</v>
+      </c>
+      <c r="AB31">
+        <v>0.03630742622486995</v>
+      </c>
+      <c r="AC31">
+        <v>24.57163492007153</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29">
       <c r="A32" s="1">
         <v>46068.56899118055</v>
       </c>
@@ -2689,14 +3190,29 @@
       <c r="U32">
         <v>676.7261030229838</v>
       </c>
-      <c r="V32">
-        <v>0.4759750499756778</v>
-      </c>
-      <c r="W32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23">
+      <c r="V32" t="b">
+        <v>1</v>
+      </c>
+      <c r="X32">
+        <v>0.240607834</v>
+      </c>
+      <c r="Y32">
+        <v>0.26095894</v>
+      </c>
+      <c r="Z32">
+        <v>0.3549530928842502</v>
+      </c>
+      <c r="AA32">
+        <v>10.175553</v>
+      </c>
+      <c r="AB32">
+        <v>0.03628799713346707</v>
+      </c>
+      <c r="AC32">
+        <v>24.55703488664037</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29">
       <c r="A33" s="1">
         <v>46068.5691069213</v>
       </c>
@@ -2760,14 +3276,29 @@
       <c r="U33">
         <v>676.5938775983371</v>
       </c>
-      <c r="V33">
-        <v>0.09012958470017536</v>
-      </c>
-      <c r="W33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23">
+      <c r="V33" t="b">
+        <v>1</v>
+      </c>
+      <c r="X33">
+        <v>0.24059673</v>
+      </c>
+      <c r="Y33">
+        <v>0.26095894</v>
+      </c>
+      <c r="Z33">
+        <v>0.3549455660416347</v>
+      </c>
+      <c r="AA33">
+        <v>10.181105</v>
+      </c>
+      <c r="AB33">
+        <v>0.03626900092660702</v>
+      </c>
+      <c r="AC33">
+        <v>24.53938397355073</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29">
       <c r="A34" s="1">
         <v>46068.56922324074</v>
       </c>
@@ -2831,14 +3362,29 @@
       <c r="U34">
         <v>678.6279979029944</v>
       </c>
-      <c r="V34">
-        <v>1.138151506564191</v>
-      </c>
-      <c r="W34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23">
+      <c r="V34" t="b">
+        <v>1</v>
+      </c>
+      <c r="X34">
+        <v>0.24057008</v>
+      </c>
+      <c r="Y34">
+        <v>0.26096435</v>
+      </c>
+      <c r="Z34">
+        <v>0.354931479812835</v>
+      </c>
+      <c r="AA34">
+        <v>10.197135</v>
+      </c>
+      <c r="AB34">
+        <v>0.03621499546303786</v>
+      </c>
+      <c r="AC34">
+        <v>24.57650986514741</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29">
       <c r="A35" s="1">
         <v>46068.56933956018</v>
       </c>
@@ -2902,14 +3448,29 @@
       <c r="U35">
         <v>678.8484977989267</v>
       </c>
-      <c r="V35">
-        <v>1.242951988000187</v>
-      </c>
-      <c r="W35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23">
+      <c r="V35" t="b">
+        <v>1</v>
+      </c>
+      <c r="X35">
+        <v>0.240546286</v>
+      </c>
+      <c r="Y35">
+        <v>0.260959258</v>
+      </c>
+      <c r="Z35">
+        <v>0.3549116087764732</v>
+      </c>
+      <c r="AA35">
+        <v>10.20648600000001</v>
+      </c>
+      <c r="AB35">
+        <v>0.03618247577132153</v>
+      </c>
+      <c r="AC35">
+        <v>24.56241932400768</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29">
       <c r="A36" s="1">
         <v>46068.56945587963</v>
       </c>
@@ -2973,14 +3534,29 @@
       <c r="U36">
         <v>678.2870699650729</v>
       </c>
-      <c r="V36">
-        <v>0.2828584085116889</v>
-      </c>
-      <c r="W36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23">
+      <c r="V36" t="b">
+        <v>1</v>
+      </c>
+      <c r="X36">
+        <v>0.240569446</v>
+      </c>
+      <c r="Y36">
+        <v>0.26095862</v>
+      </c>
+      <c r="Z36">
+        <v>0.3549268371102012</v>
+      </c>
+      <c r="AA36">
+        <v>10.194587</v>
+      </c>
+      <c r="AB36">
+        <v>0.03622291913671714</v>
+      </c>
+      <c r="AC36">
+        <v>24.56953768682563</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29">
       <c r="A37" s="1">
         <v>46068.56957219907</v>
       </c>
@@ -3044,14 +3620,29 @@
       <c r="U37">
         <v>678.0511721548928</v>
       </c>
-      <c r="V37">
-        <v>0.4095886497686853</v>
-      </c>
-      <c r="W37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23">
+      <c r="V37" t="b">
+        <v>1</v>
+      </c>
+      <c r="X37">
+        <v>0.240566908</v>
+      </c>
+      <c r="Y37">
+        <v>0.260955438</v>
+      </c>
+      <c r="Z37">
+        <v>0.3549227773001506</v>
+      </c>
+      <c r="AA37">
+        <v>10.194265</v>
+      </c>
+      <c r="AB37">
+        <v>0.03622359332043727</v>
+      </c>
+      <c r="AC37">
+        <v>24.56144991058464</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29">
       <c r="A38" s="1">
         <v>46068.56968793982</v>
       </c>
@@ -3115,14 +3706,29 @@
       <c r="U38">
         <v>680.463074158438</v>
       </c>
-      <c r="V38">
-        <v>1.329656177432138</v>
-      </c>
-      <c r="W38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23">
+      <c r="V38" t="b">
+        <v>1</v>
+      </c>
+      <c r="X38">
+        <v>0.240530422</v>
+      </c>
+      <c r="Y38">
+        <v>0.2609513</v>
+      </c>
+      <c r="Z38">
+        <v>0.3548950054300399</v>
+      </c>
+      <c r="AA38">
+        <v>10.210439</v>
+      </c>
+      <c r="AB38">
+        <v>0.03616797508935189</v>
+      </c>
+      <c r="AC38">
+        <v>24.61097151538619</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29">
       <c r="A39" s="1">
         <v>46068.56980368056</v>
       </c>
@@ -3186,14 +3792,29 @@
       <c r="U39">
         <v>680.5048141148511</v>
       </c>
-      <c r="V39">
-        <v>1.404716600500873</v>
-      </c>
-      <c r="W39" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23">
+      <c r="V39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X39">
+        <v>0.240578646</v>
+      </c>
+      <c r="Y39">
+        <v>0.26096785</v>
+      </c>
+      <c r="Z39">
+        <v>0.3549398591942244</v>
+      </c>
+      <c r="AA39">
+        <v>10.194602</v>
+      </c>
+      <c r="AB39">
+        <v>0.03622409761358244</v>
+      </c>
+      <c r="AC39">
+        <v>24.65067281300914</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29">
       <c r="A40" s="1">
         <v>46068.56992</v>
       </c>
@@ -3257,14 +3878,29 @@
       <c r="U40">
         <v>678.6853099813757</v>
       </c>
-      <c r="V40">
-        <v>1.038651608652796</v>
-      </c>
-      <c r="W40" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23">
+      <c r="V40" t="b">
+        <v>1</v>
+      </c>
+      <c r="X40">
+        <v>0.240565956</v>
+      </c>
+      <c r="Y40">
+        <v>0.260971988</v>
+      </c>
+      <c r="Z40">
+        <v>0.3549343005499273</v>
+      </c>
+      <c r="AA40">
+        <v>10.203016</v>
+      </c>
+      <c r="AB40">
+        <v>0.03619597893076973</v>
+      </c>
+      <c r="AC40">
+        <v>24.56567918070879</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29">
       <c r="A41" s="1">
         <v>46068.57003574074</v>
       </c>
@@ -3328,14 +3964,29 @@
       <c r="U41">
         <v>680.9283442046218</v>
       </c>
-      <c r="V41">
-        <v>1.191719734622256</v>
-      </c>
-      <c r="W41" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23">
+      <c r="V41" t="b">
+        <v>1</v>
+      </c>
+      <c r="X41">
+        <v>0.240522808</v>
+      </c>
+      <c r="Y41">
+        <v>0.260975808</v>
+      </c>
+      <c r="Z41">
+        <v>0.3549078662546911</v>
+      </c>
+      <c r="AA41">
+        <v>10.2265</v>
+      </c>
+      <c r="AB41">
+        <v>0.03611672618695009</v>
+      </c>
+      <c r="AC41">
+        <v>24.59290256057163</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29">
       <c r="A42" s="1">
         <v>46068.57015148148</v>
       </c>
@@ -3399,14 +4050,29 @@
       <c r="U42">
         <v>676.9237901455311</v>
       </c>
-      <c r="V42">
-        <v>2.007096072725924</v>
-      </c>
-      <c r="W42" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23">
+      <c r="V42" t="b">
+        <v>1</v>
+      </c>
+      <c r="X42">
+        <v>0.240563734</v>
+      </c>
+      <c r="Y42">
+        <v>0.260970078</v>
+      </c>
+      <c r="Z42">
+        <v>0.3549313901690703</v>
+      </c>
+      <c r="AA42">
+        <v>10.203172</v>
+      </c>
+      <c r="AB42">
+        <v>0.03619519361770408</v>
+      </c>
+      <c r="AC42">
+        <v>24.50138764874759</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29">
       <c r="A43" s="1">
         <v>46068.57026780093</v>
       </c>
@@ -3470,14 +4136,29 @@
       <c r="U43">
         <v>679.6603954057617</v>
       </c>
-      <c r="V43">
-        <v>2.046670292574219</v>
-      </c>
-      <c r="W43" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23">
+      <c r="V43" t="b">
+        <v>1</v>
+      </c>
+      <c r="X43">
+        <v>0.240522174</v>
+      </c>
+      <c r="Y43">
+        <v>0.260980262</v>
+      </c>
+      <c r="Z43">
+        <v>0.3549107117843514</v>
+      </c>
+      <c r="AA43">
+        <v>10.22904399999999</v>
+      </c>
+      <c r="AB43">
+        <v>0.03610869981774763</v>
+      </c>
+      <c r="AC43">
+        <v>24.54165319571831</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29">
       <c r="A44" s="1">
         <v>46068.57038412037</v>
       </c>
@@ -3541,14 +4222,29 @@
       <c r="U44">
         <v>680.3758120707193</v>
       </c>
-      <c r="V44">
-        <v>1.821962528283013</v>
-      </c>
-      <c r="W44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23">
+      <c r="V44" t="b">
+        <v>1</v>
+      </c>
+      <c r="X44">
+        <v>0.240501234</v>
+      </c>
+      <c r="Y44">
+        <v>0.260976762</v>
+      </c>
+      <c r="Z44">
+        <v>0.3548939473413535</v>
+      </c>
+      <c r="AA44">
+        <v>10.237764</v>
+      </c>
+      <c r="AB44">
+        <v>0.03607873070507413</v>
+      </c>
+      <c r="AC44">
+        <v>24.54709570194561</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29">
       <c r="A45" s="1">
         <v>46068.57049986111</v>
       </c>
@@ -3612,14 +4308,29 @@
       <c r="U45">
         <v>682.1009153326339</v>
       </c>
-      <c r="V45">
-        <v>1.254587567172659</v>
-      </c>
-      <c r="W45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23">
+      <c r="V45" t="b">
+        <v>1</v>
+      </c>
+      <c r="X45">
+        <v>0.240511386</v>
+      </c>
+      <c r="Y45">
+        <v>0.260990766</v>
+      </c>
+      <c r="Z45">
+        <v>0.3549111251185397</v>
+      </c>
+      <c r="AA45">
+        <v>10.23969</v>
+      </c>
+      <c r="AB45">
+        <v>0.03607407780101937</v>
+      </c>
+      <c r="AC45">
+        <v>24.60616148785596</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29">
       <c r="A46" s="1">
         <v>46068.57061618056</v>
       </c>
@@ -3683,14 +4394,29 @@
       <c r="U46">
         <v>680.1547922022721</v>
       </c>
-      <c r="V46">
-        <v>1.065537914626778</v>
-      </c>
-      <c r="W46" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23">
+      <c r="V46" t="b">
+        <v>1</v>
+      </c>
+      <c r="X46">
+        <v>0.240545968</v>
+      </c>
+      <c r="Y46">
+        <v>0.261001268</v>
+      </c>
+      <c r="Z46">
+        <v>0.3549422835034801</v>
+      </c>
+      <c r="AA46">
+        <v>10.22765</v>
+      </c>
+      <c r="AB46">
+        <v>0.03611621009355882</v>
+      </c>
+      <c r="AC46">
+        <v>24.5646133713181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29">
       <c r="A47" s="1">
         <v>46068.5707319213</v>
       </c>
@@ -3754,14 +4480,29 @@
       <c r="U47">
         <v>682.1563436257219</v>
       </c>
-      <c r="V47">
-        <v>1.139932427450089</v>
-      </c>
-      <c r="W47" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23">
+      <c r="V47" t="b">
+        <v>1</v>
+      </c>
+      <c r="X47">
+        <v>0.240496792</v>
+      </c>
+      <c r="Y47">
+        <v>0.261000314</v>
+      </c>
+      <c r="Z47">
+        <v>0.3549082569769121</v>
+      </c>
+      <c r="AA47">
+        <v>10.251761</v>
+      </c>
+      <c r="AB47">
+        <v>0.03603459914214854</v>
+      </c>
+      <c r="AC47">
+        <v>24.58123039482662</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29">
       <c r="A48" s="1">
         <v>46068.57084766203</v>
       </c>
@@ -3825,14 +4566,29 @@
       <c r="U48">
         <v>680.1296545400027</v>
       </c>
-      <c r="V48">
-        <v>1.162920795020654</v>
-      </c>
-      <c r="W48" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23">
+      <c r="V48" t="b">
+        <v>1</v>
+      </c>
+      <c r="X48">
+        <v>0.240521856</v>
+      </c>
+      <c r="Y48">
+        <v>0.260996494</v>
+      </c>
+      <c r="Z48">
+        <v>0.3549224325031834</v>
+      </c>
+      <c r="AA48">
+        <v>10.237319</v>
+      </c>
+      <c r="AB48">
+        <v>0.03608285199380214</v>
+      </c>
+      <c r="AC48">
+        <v>24.5410176613627</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29">
       <c r="A49" s="1">
         <v>46068.57096398148</v>
       </c>
@@ -3896,11 +4652,26 @@
       <c r="U49">
         <v>680.0629369228845</v>
       </c>
-      <c r="V49">
-        <v>1.189836929589439</v>
-      </c>
-      <c r="W49" t="b">
-        <v>1</v>
+      <c r="V49" t="b">
+        <v>1</v>
+      </c>
+      <c r="X49">
+        <v>0.240519318</v>
+      </c>
+      <c r="Y49">
+        <v>0.260982172</v>
+      </c>
+      <c r="Z49">
+        <v>0.3549101807965259</v>
+      </c>
+      <c r="AA49">
+        <v>10.231427</v>
+      </c>
+      <c r="AB49">
+        <v>0.03610088497292334</v>
+      </c>
+      <c r="AC49">
+        <v>24.55087386020147</v>
       </c>
     </row>
   </sheetData>
